--- a/bom-out-v0.2/示例文件/GP4.0F-完整bom.xlsx
+++ b/bom-out-v0.2/示例文件/GP4.0F-完整bom.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rust\bom-out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rust\bom-out-v0.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11505" windowHeight="9825"/>
+    <workbookView windowWidth="23745" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,21 +32,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>序号</t>
   </si>
   <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>物料编码</t>
+  </si>
+  <si>
     <t>位号</t>
   </si>
   <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>R12</t>
+    <t>cyt4bf</t>
+  </si>
+  <si>
+    <t>1111-1</t>
+  </si>
+  <si>
+    <t>U12，U12_1，U12_2，U12_3</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>222-3</t>
+  </si>
+  <si>
+    <t>C12，C12_2</t>
+  </si>
+  <si>
+    <t>100kΩ</t>
+  </si>
+  <si>
+    <t>444-5</t>
+  </si>
+  <si>
+    <t>R12,R12_1</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>123-4</t>
   </si>
   <si>
     <t>R13</t>
@@ -665,8 +695,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1194,47 +1227,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <cols>
+    <col min="4" max="4" width="34.4166666666667" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
